--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9C4EFC-C8DA-4EAD-9A76-A5925989A6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DE3BB8-07C0-432D-9BA3-7B2ECFC9A245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1377,17 +1377,19 @@
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="E13" s="14">
+        <v>78</v>
+      </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="I13" s="15">
         <f t="shared" ref="I13:I69" si="2">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>78</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" ref="J13:J69" si="3">IF(I13="","",1440-I13)</f>
-        <v/>
+        <v>1362</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DE3BB8-07C0-432D-9BA3-7B2ECFC9A245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E4C8D7-BCD5-4F66-B3DE-21C392ABE922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1380,16 +1380,18 @@
       <c r="E13" s="14">
         <v>78</v>
       </c>
-      <c r="F13" s="14"/>
+      <c r="F13" s="14">
+        <v>78</v>
+      </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="15">
         <f t="shared" ref="I13:I69" si="2">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" ref="J13:J69" si="3">IF(I13="","",1440-I13)</f>
-        <v>1362</v>
+        <v>1284</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E4C8D7-BCD5-4F66-B3DE-21C392ABE922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B5A6B3-7011-4672-8CF5-1FDA4281B058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B5A6B3-7011-4672-8CF5-1FDA4281B058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4962F1F9-72F4-4EAD-A3A2-5B90246ABBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1383,15 +1383,19 @@
       <c r="F13" s="14">
         <v>78</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="G13" s="14">
+        <v>2</v>
+      </c>
+      <c r="H13" s="14">
+        <v>100</v>
+      </c>
       <c r="I13" s="15">
         <f t="shared" ref="I13:I69" si="2">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v>156</v>
+        <v>256</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" ref="J13:J69" si="3">IF(I13="","",1440-I13)</f>
-        <v>1284</v>
+        <v>1184</v>
       </c>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4962F1F9-72F4-4EAD-A3A2-5B90246ABBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCDA20E-DE74-4746-96AB-312A24A6C8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1373,34 +1373,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
+      <c r="A13" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B13" s="14">
+        <v>240</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>45</v>
+      </c>
       <c r="E13" s="14">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="F13" s="14">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="G13" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" ref="I13:I69" si="2">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v>256</v>
+        <v>705</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" ref="J13:J69" si="3">IF(I13="","",1440-I13)</f>
-        <v>1184</v>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>735</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCDA20E-DE74-4746-96AB-312A24A6C8A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9370F6C-EE96-4A08-9611-D1587819F919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>August</t>
+  </si>
+  <si>
+    <t>Attended guests and visited gaming zone with them</t>
   </si>
 </sst>
 </file>
@@ -1418,27 +1421,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B14" s="14">
+        <v>360</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>240</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>180</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9370F6C-EE96-4A08-9611-D1587819F919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4083F930-8B1D-44B8-8919-507E1854A60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t>Attended guests and visited gaming zone with them</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A very close friend went abroad for studies </t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1444,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="14">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G14" s="14">
         <v>4</v>
@@ -1448,11 +1454,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>860</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="3"/>
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>49</v>
@@ -1467,27 +1473,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>150</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="14">
+        <v>240</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4083F930-8B1D-44B8-8919-507E1854A60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068364C9-6F92-4B03-B234-7B77F41B0FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1520,26 +1520,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>300</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068364C9-6F92-4B03-B234-7B77F41B0FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9352B020-9B12-4BE4-AE3A-5F5464F8A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t xml:space="preserve">A very close friend went abroad for studies </t>
+  </si>
+  <si>
+    <t>Went to a famous temple in our neighbouring city with family</t>
   </si>
 </sst>
 </file>
@@ -1565,27 +1568,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>240</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>240</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9352B020-9B12-4BE4-AE3A-5F5464F8A1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FB0289-0336-4ACF-8F64-4240A53FF4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1615,26 +1615,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B18" s="14">
+        <v>300</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>20</v>
+      </c>
+      <c r="F18" s="14">
+        <v>150</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="14">
+        <v>300</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FB0289-0336-4ACF-8F64-4240A53FF4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172B37E0-624B-46E2-B595-010F5B2E676B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Went to a famous temple in our neighbouring city with family</t>
+  </si>
+  <si>
+    <t>Me and my father went to moga city for a business visit</t>
   </si>
 </sst>
 </file>
@@ -1660,27 +1663,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>50</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>240</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12610630.xlsx
+++ b/12610630.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mohit\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172B37E0-624B-46E2-B595-010F5B2E676B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5C9567-B340-4FEB-9CBC-390B885A666D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,12 @@
   </si>
   <si>
     <t>Me and my father went to moga city for a business visit</t>
+  </si>
+  <si>
+    <t>Like a regular Tuesday, I visitem temple and performed volunatry service</t>
+  </si>
+  <si>
+    <t>was busy in preparations mostly for my cousin's surprise birthday party</t>
   </si>
 </sst>
 </file>
@@ -1663,7 +1669,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>46266</v>
       </c>
@@ -1706,55 +1712,105 @@
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B20" s="14">
+        <v>540</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>240</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>200</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" si="2"/>
+        <v>1230</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" si="3"/>
+        <v>210</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="21" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B21" s="14">
+        <v>540</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>250</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="13">
+        <v>46269</v>
+      </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
